--- a/www/terminologies/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/www/terminologies/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -99,13 +99,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R357-StatutPersonnePriseCharge/FHIR/TRE-R357-StatutPersonnePriseCharge|20231215120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R357-StatutPersonnePriseCharge/FHIR/TRE-R357-StatutPersonnePriseCharge</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R358-MotifStatutPersonnePriseCharge/FHIR/TRE-R358-MotifStatutPersonnePriseCharge|20231215120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R358-MotifStatutPersonnePriseCharge/FHIR/TRE-R358-MotifStatutPersonnePriseCharge</t>
   </si>
   <si>
     <t>181</t>
